--- a/R_sediment_traps/init_files/division_palette.xlsx
+++ b/R_sediment_traps/init_files/division_palette.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10512"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deniseong/Documents/GitHub/Cruise-New-Zealand-TAN1810/R_sediment_traps/init_files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deniseong/Documents/GitHub/TAN1810_sedtraps/R_sediment_traps/init_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3F2038-5B79-084A-B8DF-4D974A4617D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09CA15F4-F16E-354F-9217-9C7F9975D8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3100" yWindow="780" windowWidth="20720" windowHeight="19900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19080" yWindow="780" windowWidth="20720" windowHeight="19900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$32</definedName>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="90">
   <si>
     <t>Dinoflagellata</t>
   </si>
@@ -236,6 +237,63 @@
   </si>
   <si>
     <t>not shared</t>
+  </si>
+  <si>
+    <t>order</t>
+  </si>
+  <si>
+    <t>Dino-Group-I</t>
+  </si>
+  <si>
+    <t>Dino-Group-II</t>
+  </si>
+  <si>
+    <t>Dino-Group-III</t>
+  </si>
+  <si>
+    <t>Dinophyceae_X</t>
+  </si>
+  <si>
+    <t>Gonyaulacales</t>
+  </si>
+  <si>
+    <t>Gymnodiniales</t>
+  </si>
+  <si>
+    <t>Peridiniales</t>
+  </si>
+  <si>
+    <t>Suessiales</t>
+  </si>
+  <si>
+    <t>Noctilucales</t>
+  </si>
+  <si>
+    <t>#E1BEE7</t>
+  </si>
+  <si>
+    <t>#9C27B0</t>
+  </si>
+  <si>
+    <t>#6A1B9A</t>
+  </si>
+  <si>
+    <t>#DEEBF7</t>
+  </si>
+  <si>
+    <t>#9ECAE1</t>
+  </si>
+  <si>
+    <t>#4292C6</t>
+  </si>
+  <si>
+    <t>#08519C</t>
+  </si>
+  <si>
+    <t>#08306B</t>
+  </si>
+  <si>
+    <t>#01665E</t>
   </si>
 </sst>
 </file>
@@ -892,4 +950,97 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2662E23-8382-3D47-A73B-C25DF6A8374F}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>